--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N173_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N173_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.82216158774714</v>
+        <v>10.37110125800891</v>
       </c>
       <c r="D2" t="n">
-        <v>62.0950093364433</v>
+        <v>10.09043901717204</v>
       </c>
       <c r="E2" t="n">
-        <v>21.55305549671506</v>
+        <v>3.502371518216198</v>
       </c>
       <c r="F2" t="n">
-        <v>17.72653775507604</v>
+        <v>2.880562385199856</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.6271124853878</v>
+        <v>10.33940577887552</v>
       </c>
       <c r="D3" t="n">
-        <v>62.06479123747031</v>
+        <v>10.08552857608893</v>
       </c>
       <c r="E3" t="n">
-        <v>21.55305549671506</v>
+        <v>3.502371518216198</v>
       </c>
       <c r="F3" t="n">
-        <v>17.72653775507604</v>
+        <v>2.880562385199856</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.18374381414813</v>
+        <v>4.092358369799071</v>
       </c>
       <c r="D4" t="n">
-        <v>25.31451978329653</v>
+        <v>4.113609464785687</v>
       </c>
       <c r="E4" t="n">
-        <v>21.55305549671506</v>
+        <v>3.502371518216198</v>
       </c>
       <c r="F4" t="n">
-        <v>17.72653775507604</v>
+        <v>2.880562385199856</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.8811135961671</v>
+        <v>1.768180959377154</v>
       </c>
       <c r="D5" t="n">
-        <v>6.060115794443377</v>
+        <v>0.9847688165970487</v>
       </c>
       <c r="E5" t="n">
-        <v>21.55305549671506</v>
+        <v>3.502371518216198</v>
       </c>
       <c r="F5" t="n">
-        <v>17.72653775507604</v>
+        <v>2.880562385199856</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.84258714109455</v>
+        <v>3.549420410427864</v>
       </c>
       <c r="D6" t="n">
-        <v>24.83943610308601</v>
+        <v>4.036408366751477</v>
       </c>
       <c r="E6" t="n">
-        <v>21.55305549671506</v>
+        <v>3.502371518216198</v>
       </c>
       <c r="F6" t="n">
-        <v>17.72653775507604</v>
+        <v>2.880562385199856</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.53096438833628</v>
+        <v>1.386281713104645</v>
       </c>
       <c r="D7" t="n">
-        <v>15.01293510765051</v>
+        <v>2.439601954993209</v>
       </c>
       <c r="E7" t="n">
-        <v>21.55305549671506</v>
+        <v>3.502371518216198</v>
       </c>
       <c r="F7" t="n">
-        <v>17.72653775507604</v>
+        <v>2.880562385199856</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>59.73313071256867</v>
+        <v>9.706633740792409</v>
       </c>
       <c r="D8" t="n">
-        <v>58.98239381171739</v>
+        <v>9.584638994404077</v>
       </c>
       <c r="E8" t="n">
-        <v>21.55305549671506</v>
+        <v>3.502371518216198</v>
       </c>
       <c r="F8" t="n">
-        <v>17.72653775507604</v>
+        <v>2.880562385199856</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.3468487053198</v>
+        <v>2.656362914614468</v>
       </c>
       <c r="D9" t="n">
-        <v>40.52750276226651</v>
+        <v>6.585719198868308</v>
       </c>
       <c r="E9" t="n">
-        <v>21.55305549671506</v>
+        <v>3.502371518216198</v>
       </c>
       <c r="F9" t="n">
-        <v>17.72653775507604</v>
+        <v>2.880562385199856</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.4547926718107</v>
+        <v>3.97390380916924</v>
       </c>
       <c r="D10" t="n">
-        <v>56.13741546064289</v>
+        <v>9.122330012354471</v>
       </c>
       <c r="E10" t="n">
-        <v>21.55305549671506</v>
+        <v>3.502371518216198</v>
       </c>
       <c r="F10" t="n">
-        <v>17.72653775507604</v>
+        <v>2.880562385199856</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.29972343472674</v>
+        <v>5.086205058143094</v>
       </c>
       <c r="D11" t="n">
-        <v>46.26982257051991</v>
+        <v>7.518846167709486</v>
       </c>
       <c r="E11" t="n">
-        <v>21.55305549671506</v>
+        <v>3.502371518216198</v>
       </c>
       <c r="F11" t="n">
-        <v>17.72653775507604</v>
+        <v>2.880562385199856</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>43.59209859408722</v>
+        <v>7.083716021539173</v>
       </c>
       <c r="D12" t="n">
-        <v>43.26653243885616</v>
+        <v>7.030811521314126</v>
       </c>
       <c r="E12" t="n">
-        <v>21.55305549671506</v>
+        <v>3.502371518216198</v>
       </c>
       <c r="F12" t="n">
-        <v>17.72653775507604</v>
+        <v>2.880562385199856</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>33.35383524210032</v>
+        <v>5.419998226841303</v>
       </c>
       <c r="D13" t="n">
-        <v>33.71243045638369</v>
+        <v>5.478269949162351</v>
       </c>
       <c r="E13" t="n">
-        <v>21.55305549671506</v>
+        <v>3.502371518216198</v>
       </c>
       <c r="F13" t="n">
-        <v>17.72653775507604</v>
+        <v>2.880562385199856</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>36.92206475010649</v>
+        <v>5.999835521892305</v>
       </c>
       <c r="D14" t="n">
-        <v>29.7069015550259</v>
+        <v>4.827371502691708</v>
       </c>
       <c r="E14" t="n">
-        <v>21.55305549671506</v>
+        <v>3.502371518216198</v>
       </c>
       <c r="F14" t="n">
-        <v>17.72653775507604</v>
+        <v>2.880562385199856</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>48.10467574954596</v>
+        <v>7.817009809301219</v>
       </c>
       <c r="D15" t="n">
-        <v>12.85112783068218</v>
+        <v>2.088308272485855</v>
       </c>
       <c r="E15" t="n">
-        <v>21.55305549671506</v>
+        <v>3.502371518216198</v>
       </c>
       <c r="F15" t="n">
-        <v>17.72653775507604</v>
+        <v>2.880562385199856</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>85.85881756127969</v>
+        <v>13.95205785370795</v>
       </c>
       <c r="D16" t="n">
-        <v>47.06611257767186</v>
+        <v>7.648243293871677</v>
       </c>
       <c r="E16" t="n">
-        <v>21.55305549671506</v>
+        <v>3.502371518216198</v>
       </c>
       <c r="F16" t="n">
-        <v>17.72653775507604</v>
+        <v>2.880562385199856</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
